--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -370,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -500,6 +500,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -977,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="50">
       <c r="A3" s="43" t="inlineStr">
         <is>
           <t>1. 인증 (Authentication)</t>
@@ -14885,169 +14889,172 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="233" s="50">
+      <c r="A233" s="57" t="inlineStr">
         <is>
           <t>14. 성능 / 번들 최적화 (Performance)</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="234" ht="36" customHeight="1" s="50">
+      <c r="A234" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>TC-FE-PERF-001</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>ProjectPage</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>lazy import</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>탭 컴포넌트 lazy 로딩 확인</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
+      <c r="H234" s="3" t="inlineStr">
         <is>
           <t>1. 프로젝트 페이지 진입
 2. Network 탭에서 chunk 로딩 확인
 3. 탭 전환</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I234" s="3" t="inlineStr">
         <is>
           <t>1. 활성 탭 chunk만 로드
 2. 탭 전환 시 해당 chunk 추가 로드</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
+      <c r="J234" s="3" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="K234" s="2" t="n"/>
+    </row>
+    <row r="235" ht="36" customHeight="1" s="50">
+      <c r="A235" s="2" t="n">
         <v>207</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>TC-FE-PERF-002</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>ProjectPage</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Suspense fallback</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>느린 네트워크에서 로딩 UI 표시</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H235" s="3" t="inlineStr">
         <is>
           <t>1. Network throttle 적용
 2. 프로젝트 탭 전환</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I235" s="3" t="inlineStr">
         <is>
           <t>1. 로딩 중 fallback 텍스트 표시
 2. chunk 로드 후 컴포넌트 정상 렌더링</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
+      <c r="J235" s="3" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
+      <c r="K235" s="2" t="n"/>
+    </row>
+    <row r="236" ht="36" customHeight="1" s="50">
+      <c r="A236" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>TC-FE-PERF-003</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>빌드</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>chunk 분리</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>vite build 청크 분리 확인</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
+      <c r="H236" s="3" t="inlineStr">
         <is>
           <t>1. npm run build 실행
 2. dist/assets 확인</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I236" s="3" t="inlineStr">
         <is>
           <t>1. vendor/grid/charts/i18n/utils 별도 chunk 존재
 2. index &lt; 500KB</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
+      <c r="J236" s="3" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
+      <c r="K236" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:O2"/>
@@ -15196,7 +15203,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="50">
       <c r="A3" s="53" t="inlineStr">
         <is>
           <t>1. 인증 (Authentication)</t>
@@ -15218,7 +15225,7 @@
       <c r="O3" s="47" t="n"/>
       <c r="P3" s="48" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" s="50">
       <c r="A4" s="16" t="n">
         <v>1</v>
       </c>
@@ -27561,463 +27568,482 @@
       <c r="M228" s="38" t="n"/>
       <c r="N228" s="38" t="n"/>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="229" s="50">
+      <c r="A229" s="58" t="inlineStr">
         <is>
           <t>15. 성능 최적화 (Performance)</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="n">
+    <row r="230" s="50">
+      <c r="A230" s="16" t="n">
         <v>207</v>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-001</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C230" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D230" s="16" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E230" s="16" t="inlineStr">
         <is>
           <t>SQL 집계</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="F230" s="16" t="n"/>
+      <c r="G230" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H230" s="17" t="inlineStr">
         <is>
           <t>v1.1.0.1 SQL CASE+GROUP BY</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I230" s="17" t="inlineStr">
         <is>
           <t>GET /dashboard/summary 호출</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr">
+      <c r="J230" s="17" t="inlineStr">
         <is>
           <t>응답 200, SQL 집계 결과 반환 (ORM 전체 로드 없음)</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="K230" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="n">
+    <row r="231" s="50">
+      <c r="A231" s="16" t="n">
         <v>208</v>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-002</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C231" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D231" s="16" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E231" s="16" t="inlineStr">
         <is>
           <t>priority/category/assignee</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="F231" s="16" t="n"/>
+      <c r="G231" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="H231" s="17" t="n"/>
+      <c r="I231" s="17" t="inlineStr">
         <is>
           <t>GET /dashboard/priority, /category, /assignee 호출</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr">
+      <c r="J231" s="17" t="inlineStr">
         <is>
           <t>각 엔드포인트 200 응답, 데이터 정합성 확인</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="K231" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="n">
+    <row r="232" s="50">
+      <c r="A232" s="16" t="n">
         <v>209</v>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-003</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C232" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D232" s="16" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" s="16" t="inlineStr">
         <is>
           <t>rounds SQL 집계</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="F232" s="16" t="n"/>
+      <c r="G232" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="H232" s="17" t="n"/>
+      <c r="I232" s="17" t="inlineStr">
         <is>
           <t>GET /dashboard/rounds 호출</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
+      <c r="J232" s="17" t="inlineStr">
         <is>
           <t>라운드별 PASS/FAIL 카운트가 기존과 동일</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="K232" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="n">
+    <row r="233" s="50">
+      <c r="A233" s="16" t="n">
         <v>210</v>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-004</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D233" s="16" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E233" s="16" t="inlineStr">
         <is>
           <t>SQL 집계</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="F233" s="16" t="n"/>
+      <c r="G233" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="H233" s="17" t="n"/>
+      <c r="I233" s="17" t="inlineStr">
         <is>
           <t>GET /api/dashboard/overview 호출</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
+      <c r="J233" s="17" t="inlineStr">
         <is>
           <t>프로젝트별 TC 수, PASS/FAIL 카운트 정상</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="K233" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="234" s="50">
+      <c r="A234" s="16" t="n">
         <v>211</v>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-005</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" s="16" t="inlineStr">
         <is>
           <t>TestPlan</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="16" t="inlineStr">
         <is>
           <t>N+1 제거</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="F234" s="16" t="n"/>
+      <c r="G234" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="H234" s="17" t="n"/>
+      <c r="I234" s="17" t="inlineStr">
         <is>
           <t>GET /testplans 플랜 목록 조회</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
+      <c r="J234" s="17" t="inlineStr">
         <is>
           <t>run_count, progress가 기존과 동일 (SQL 2회)</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="K234" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="235" s="50">
+      <c r="A235" s="16" t="n">
         <v>212</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-006</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="16" t="inlineStr">
         <is>
           <t>TestRun</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" s="16" t="inlineStr">
         <is>
           <t>bulk insert</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="F235" s="16" t="n"/>
+      <c r="G235" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="H235" s="17" t="n"/>
+      <c r="I235" s="17" t="inlineStr">
         <is>
           <t>POST /testruns 생성 후 결과 수 확인</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
+      <c r="J235" s="17" t="inlineStr">
         <is>
           <t>TC 수와 동일한 TestResult 생성, 모두 NS</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K235" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="236" s="50">
+      <c r="A236" s="16" t="n">
         <v>213</v>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-007</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="16" t="inlineStr">
         <is>
           <t>TestRun</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="16" t="inlineStr">
         <is>
           <t>clone bulk insert</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="F236" s="16" t="n"/>
+      <c r="G236" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="H236" s="17" t="n"/>
+      <c r="I236" s="17" t="inlineStr">
         <is>
           <t>POST /testruns/{id}/clone 복제</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
+      <c r="J236" s="17" t="inlineStr">
         <is>
           <t>복제 런의 결과 수 = 원본 결과 수, 모두 NS</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="K236" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="n">
+    <row r="237" s="50">
+      <c r="A237" s="16" t="n">
         <v>214</v>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-008</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D237" s="16" t="inlineStr">
         <is>
           <t>결과 제출</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" s="16" t="inlineStr">
         <is>
           <t>IN prefetch</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="F237" s="16" t="n"/>
+      <c r="G237" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="H237" s="17" t="n"/>
+      <c r="I237" s="17" t="inlineStr">
         <is>
           <t>POST /testruns/{id}/results 다건 제출</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr">
+      <c r="J237" s="17" t="inlineStr">
         <is>
           <t>결과 정상 저장, N+1 없이 응답</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="K237" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="n">
+    <row r="238" s="50">
+      <c r="A238" s="16" t="n">
         <v>215</v>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-009</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" s="16" t="inlineStr">
         <is>
           <t>리포트</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" s="16" t="inlineStr">
         <is>
           <t>SQL 집계 + 이중로드 제거</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="F238" s="16" t="n"/>
+      <c r="G238" s="16" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="H238" s="17" t="n"/>
+      <c r="I238" s="17" t="inlineStr">
         <is>
           <t>GET /reports, /reports/pdf, /reports/excel 호출</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
+      <c r="J238" s="17" t="inlineStr">
         <is>
           <t>JSON/PDF/Excel 정상 생성, summary 수치 일치</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="K238" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="239" s="50">
+      <c r="A239" s="16" t="n">
         <v>216</v>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="16" t="inlineStr">
         <is>
           <t>TC-BE-PERF-010</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="16" t="inlineStr">
         <is>
           <t>성능</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" s="16" t="inlineStr">
         <is>
           <t>WAL 모드</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="16" t="inlineStr">
         <is>
           <t>SQLite PRAGMA</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="F239" s="16" t="n"/>
+      <c r="G239" s="16" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="H239" s="17" t="n"/>
+      <c r="I239" s="17" t="inlineStr">
         <is>
           <t>서버 시작 후 PRAGMA journal_mode 확인</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
+      <c r="J239" s="17" t="inlineStr">
         <is>
           <t>WAL 모드 활성화 확인</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K239" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P236"/>
+  <dimension ref="A1:P240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15055,6 +15055,302 @@
         </is>
       </c>
       <c r="K236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-033</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>시트 탭</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>런 생성 이후 추가 TC</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="n"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>진행 중인 런이 존재할 것</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr">
+        <is>
+          <t>1. 테스트 런을 생성한다.
+2. 런 생성 후 새 시트를 만들고 TC 를 추가한다.
+3. 테스트 수행 화면에서 해당 시트 탭을 클릭한다.</t>
+        </is>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t>1. 추가한 TC 가 그리드에 미입력 상태로 표시된다.
+2. 탭 배지 숫자와 그리드 행 수가 일치한다.</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-034</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>시트 탭</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>결과 0건 시트 선택</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="n"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>결과가 0건인 시트가 존재할 것 (완료된 런에서 재현)</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>1. 결과가 0건인 시트 탭을 클릭한다.
+2. 하단 시트 탭 바를 확인한다.
+3. 다른 시트 탭을 클릭해 되돌아간다.</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>1. 그리드는 비어 있으나 시트 탭 바는 유지된다.
+2. 다른 시트로 되돌아갈 수 있다.
+3. 새로고침 없이 이동이 가능하다.</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-035</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>시트 탭</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>배지 숫자 기준</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="n"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>완료된 런에 그 이후 추가된 TC 가 있을 것</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>1. 완료된 런을 연다.
+2. 런 완료 후 추가된 TC 가 있는 시트 탭 배지를 확인한다.</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t>1. 배지는 TC 라이브러리 수가 아니라 해당 런의 결과 수를 표시한다.
+2. 배지 숫자와 그리드 행 수가 일치한다.</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-036</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>시트 탭</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>TC 번호 정렬</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="n"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>런 생성 이후 기존 TC 사이에 끼는 번호로 TC 를 추가할 것</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>1. TC 번호 1, 3 을 만들고 런을 생성한다.
+2. 런 생성 후 번호 2 로 TC 를 추가한다.
+3. 해당 시트 탭에서 행 순서를 확인한다.</t>
+        </is>
+      </c>
+      <c r="J240" s="3" t="inlineStr">
+        <is>
+          <t>1. 1, 2, 3 순서로 표시된다.
+2. 나중에 편입된 TC 가 맨 뒤로 밀리지 않는다.</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:O2"/>
@@ -15091,7 +15387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P239"/>
+  <dimension ref="A1:P245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -28046,6 +28342,443 @@
       <c r="K239" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="16" t="n">
+        <v>217</v>
+      </c>
+      <c r="B240" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-SYNC-001</t>
+        </is>
+      </c>
+      <c r="C240" s="16" t="inlineStr">
+        <is>
+          <t>런 동기화</t>
+        </is>
+      </c>
+      <c r="D240" s="16" t="inlineStr">
+        <is>
+          <t>진행 중 런</t>
+        </is>
+      </c>
+      <c r="E240" s="16" t="inlineStr">
+        <is>
+          <t>누락 TC 흡수</t>
+        </is>
+      </c>
+      <c r="F240" s="16" t="n"/>
+      <c r="G240" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H240" s="17" t="inlineStr">
+        <is>
+          <t>진행 중인 런이 존재할 것</t>
+        </is>
+      </c>
+      <c r="I240" s="17" t="inlineStr">
+        <is>
+          <t>GET /api/projects/{pid}/testruns/{id} 조회 및 TC 생성 후 결과 행 확인</t>
+        </is>
+      </c>
+      <c r="J240" s="17" t="inlineStr">
+        <is>
+          <t>1. 런 생성 이후 추가된 TC 의 결과 행이 NS 로 생성된다.
+2. 반복 조회해도 중복 생성되지 않는다.</t>
+        </is>
+      </c>
+      <c r="K240" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="16" t="n">
+        <v>218</v>
+      </c>
+      <c r="B241" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-SYNC-002</t>
+        </is>
+      </c>
+      <c r="C241" s="16" t="inlineStr">
+        <is>
+          <t>런 동기화</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>완료 런</t>
+        </is>
+      </c>
+      <c r="E241" s="16" t="inlineStr">
+        <is>
+          <t>스냅샷 유지</t>
+        </is>
+      </c>
+      <c r="F241" s="16" t="n"/>
+      <c r="G241" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H241" s="17" t="inlineStr">
+        <is>
+          <t>완료 상태의 런이 존재할 것</t>
+        </is>
+      </c>
+      <c r="I241" s="17" t="inlineStr">
+        <is>
+          <t>런을 완료 처리한 뒤 TC 를 추가하고 런 상세를 조회</t>
+        </is>
+      </c>
+      <c r="J241" s="17" t="inlineStr">
+        <is>
+          <t>1. 완료된 런은 이후 추가된 TC 를 흡수하지 않는다.
+2. 생성 당시 스냅샷이 유지된다.</t>
+        </is>
+      </c>
+      <c r="K241" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="16" t="n">
+        <v>219</v>
+      </c>
+      <c r="B242" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-SYNC-003</t>
+        </is>
+      </c>
+      <c r="C242" s="16" t="inlineStr">
+        <is>
+          <t>런 동기화</t>
+        </is>
+      </c>
+      <c r="D242" s="16" t="inlineStr">
+        <is>
+          <t>reopen</t>
+        </is>
+      </c>
+      <c r="E242" s="16" t="inlineStr">
+        <is>
+          <t>완료 기간 추가분 흡수</t>
+        </is>
+      </c>
+      <c r="F242" s="16" t="n"/>
+      <c r="G242" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H242" s="17" t="inlineStr">
+        <is>
+          <t>완료 상태에서 TC 가 추가되었을 것</t>
+        </is>
+      </c>
+      <c r="I242" s="17" t="inlineStr">
+        <is>
+          <t>PUT /api/projects/{pid}/testruns/{id}/reopen 후 상세 조회 없이 리포트 확인</t>
+        </is>
+      </c>
+      <c r="J242" s="17" t="inlineStr">
+        <is>
+          <t>1. reopen 시점에 누락 TC 가 흡수된다.
+2. 상세를 열지 않고 완료해도 누락되지 않는다.</t>
+        </is>
+      </c>
+      <c r="K242" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="16" t="n">
+        <v>220</v>
+      </c>
+      <c r="B243" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-SYNC-004</t>
+        </is>
+      </c>
+      <c r="C243" s="16" t="inlineStr">
+        <is>
+          <t>런 동기화</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="E243" s="16" t="inlineStr">
+        <is>
+          <t>viewer 쓰기 차단</t>
+        </is>
+      </c>
+      <c r="F243" s="16" t="n"/>
+      <c r="G243" s="16" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="H243" s="17" t="inlineStr">
+        <is>
+          <t>공개 프로젝트이고 조회자가 viewer 일 것</t>
+        </is>
+      </c>
+      <c r="I243" s="17" t="inlineStr">
+        <is>
+          <t>viewer 권한으로 런 상세를 조회하고 test_results 변화를 확인</t>
+        </is>
+      </c>
+      <c r="J243" s="17" t="inlineStr">
+        <is>
+          <t>1. viewer 조회만으로는 결과 행이 생성되지 않는다.
+2. tester 이상에서만 보정이 수행된다.</t>
+        </is>
+      </c>
+      <c r="K243" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>수동</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="B244" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-SYNC-005</t>
+        </is>
+      </c>
+      <c r="C244" s="16" t="inlineStr">
+        <is>
+          <t>런 동기화</t>
+        </is>
+      </c>
+      <c r="D244" s="16" t="inlineStr">
+        <is>
+          <t>리포트 정합성</t>
+        </is>
+      </c>
+      <c r="E244" s="16" t="inlineStr">
+        <is>
+          <t>상세 미조회 상태</t>
+        </is>
+      </c>
+      <c r="F244" s="16" t="n"/>
+      <c r="G244" s="16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H244" s="17" t="inlineStr">
+        <is>
+          <t>런 상세를 한 번도 호출하지 않았을 것</t>
+        </is>
+      </c>
+      <c r="I244" s="17" t="inlineStr">
+        <is>
+          <t>TC 추가 후 런 상세 없이 GET /api/projects/{pid}/reports 조회</t>
+        </is>
+      </c>
+      <c r="J244" s="17" t="inlineStr">
+        <is>
+          <t>1. 리포트 total 이 추가된 TC 를 포함한다.
+2. 런을 열기 전과 후의 수치가 같다.</t>
+        </is>
+      </c>
+      <c r="K244" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="16" t="n">
+        <v>222</v>
+      </c>
+      <c r="B245" s="16" t="inlineStr">
+        <is>
+          <t>TC-BE-PERF-011</t>
+        </is>
+      </c>
+      <c r="C245" s="16" t="inlineStr">
+        <is>
+          <t>성능</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="inlineStr">
+        <is>
+          <t>busy_timeout</t>
+        </is>
+      </c>
+      <c r="E245" s="16" t="inlineStr">
+        <is>
+          <t>SQLite PRAGMA</t>
+        </is>
+      </c>
+      <c r="F245" s="16" t="n"/>
+      <c r="G245" s="16" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="H245" s="17" t="n"/>
+      <c r="I245" s="17" t="inlineStr">
+        <is>
+          <t>서버 시작 후 PRAGMA busy_timeout 확인</t>
+        </is>
+      </c>
+      <c r="J245" s="17" t="inlineStr">
+        <is>
+          <t>busy_timeout 이 30000ms 로 설정되어 있다.</t>
+        </is>
+      </c>
+      <c r="K245" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프론트엔드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="백엔드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인코딩이슈추적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="프론트엔드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="백엔드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="인코딩이슈추적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="요약" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'프론트엔드'!$A$2:$O$2</definedName>
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P240"/>
+  <dimension ref="A1:P241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15278,7 +15278,7 @@
         </is>
       </c>
     </row>
-    <row r="240">
+    <row r="240" s="50">
       <c r="A240" s="2" t="n">
         <v>212</v>
       </c>
@@ -15349,6 +15349,76 @@
       <c r="O240" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" s="50">
+      <c r="A241" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-037</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>첨부파일</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>목록 표시</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="n"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>결과 행에 첨부파일이 있는 런. 업로드 직후가 아니라 페이지를 새로고침한 뒤 확인한다.</t>
+        </is>
+      </c>
+      <c r="I241" s="3" t="inlineStr">
+        <is>
+          <t>1. 첨부파일이 있는 런을 새로 연다.
+2. 첨부파일 컬럼을 클릭하지 않은 상태로 그리드를 본다.</t>
+        </is>
+      </c>
+      <c r="J241" s="3" t="inlineStr">
+        <is>
+          <t>1. 첨부가 있는 행에 파일명이 바로 표시된다.
+2. 첨부가 없는 행에는 + 버튼만 표시된다.
+3. 첨부 유무를 알기 위해 셀을 클릭할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="n"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>SYM-36. 자동화: frontend TestRunAttachments.test.tsx</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P241"/>
+  <dimension ref="A1:P246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15417,6 +15417,361 @@
         </is>
       </c>
       <c r="P241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" s="50">
+      <c r="A242" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-038</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>시트 선택</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>일부 시트로 생성</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="n"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>시트가 2개 이상이고 각 시트에 TC 가 있는 프로젝트.</t>
+        </is>
+      </c>
+      <c r="I242" s="3" t="inlineStr">
+        <is>
+          <t>1. 새 테스트 수행 만들기를 연다.
+2. 포함할 시트에서 일부 시트의 체크를 푼다.
+3. 수행 이름을 넣고 생성한다.</t>
+        </is>
+      </c>
+      <c r="J242" s="3" t="inlineStr">
+        <is>
+          <t>1. 처음에는 모든 시트가 선택되어 있다.
+2. 체크를 푼 시트의 TC 는 수행에 담기지 않는다.
+3. 시트 탭에 고른 시트만 나온다.
+4. 전부 해제하면 생성 버튼이 잠긴다.</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="n"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>SYM-37. 자동화: TestRunSheetScope.test.tsx / test_run_sheet_scope.py</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" s="50">
+      <c r="A243" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-039</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>시트 선택</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>범위 밖 TC 유입 차단</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="n"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>일부 시트만 담은 진행 중 수행이 있다.</t>
+        </is>
+      </c>
+      <c r="I243" s="3" t="inlineStr">
+        <is>
+          <t>1. 그 수행의 범위 밖 시트에 TC 를 새로 만든다.
+2. 범위 안 시트에도 TC 를 새로 만든다.
+3. 수행을 다시 연다.</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
+        <is>
+          <t>1. 범위 안에 만든 TC 는 수행에 들어온다.
+2. 범위 밖에 만든 TC 는 들어오지 않는다.
+3. 시트 탭 구성이 그대로다.</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="n"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>SYM-37</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" s="50">
+      <c r="A244" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-040</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>시트 선택</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>대시보드 진행률</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="n"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>일부 시트만 담은 수행이 있고 그 수행의 TC 를 전부 PASS 로 입력했다.</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>1. 대시보드에서 그 수행을 고른다.
+2. 총 건수와 진행률을 본다.</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t>1. 총 건수가 그 수행이 담은 TC 수와 같다.
+2. 진행률 100%, 미실행 0 이다.
+3. 프로젝트 전체 TC 수가 분모로 쓰이지 않는다.</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="n"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>SYM-38</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" s="50">
+      <c r="A245" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-041</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>시트 선택</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>시트 이름 변경 후 범위 유지</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="n"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>일부 시트만 담은 진행 중 수행이 있다.</t>
+        </is>
+      </c>
+      <c r="I245" s="3" t="inlineStr">
+        <is>
+          <t>1. 그 수행이 담은 시트의 이름을 바꾼다.
+2. 수행으로 돌아가 결과를 입력한다.
+3. 이름이 바뀐 시트에 TC 를 새로 만든다.</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>1. 결과가 정상 저장된다.
+2. 새로 만든 TC 가 수행에 들어온다.
+3. 시트 탭이 바뀐 이름으로 보인다.</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="n"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>SYM-37</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" s="50">
+      <c r="A246" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>TC-TR-042</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>결과 저장</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>거부 시 사유 표시와 원복</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="n"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>결과 저장이 거부되는 상황(예: 시트 범위 밖 TC).</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>1. 저장이 거부되는 값을 입력한다.
+2. 토스트 문구를 확인한다.
+3. 화면의 셀 값을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>1. 서버가 준 사유가 그대로 뜬다. '저장 실패' 로 뭉개지 않는다.
+2. 화면 값이 서버 값으로 돌아간다.
+3. 새로고침해도 같은 값이다.</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="n"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>SYM-40. 자동화: TestRunSaveError.test.tsx</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P246"/>
+  <dimension ref="A1:P249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15772,6 +15772,211 @@
         </is>
       </c>
       <c r="P246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>TC-RPT-007</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>요약 카드</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>미수행/N-A 노출</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>미수행(NS) 결과가 1건 이상 남은 런</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 해당 런을 선택한다.
+2. 전체 현황 카드를 확인한다.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>1. 전체 TC/PASS/FAIL/BLOCK/N-A/미수행/PASS Rate 카드가 표시된다.
+2. PASS+FAIL+BLOCK+N-A+미수행 합이 전체 TC 와 같다.
+3. PASS Rate 카드 아래에 분모가 실행 건수임이 표기된다.</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TC-RPT-008</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>카테고리별 요약</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>미수행 컬럼</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>카테고리가 2개 이상이고 미수행이 남은 런</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 해당 런을 선택한다.
+2. 카테고리별 요약 표를 확인한다.</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>1. Total/PASS/FAIL/BLOCK/N-A/미수행 컬럼이 모두 표시된다.
+2. 각 행에서 PASS+FAIL+BLOCK+N-A+미수행 합이 Total 과 같다.</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TC-RPT-009</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>리포트</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>카테고리 표 컬럼</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>미수행이 남은 런</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>1. PDF 다운로드 버튼을 클릭한다.
+2. PDF 의 Category Breakdown 표를 확인한다.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>1. Category/Total/Pass/Fail/Block/NA/NS 컬럼이 표시된다.
+2. 표가 페이지 폭을 넘지 않는다.</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/TC_Manager_Regression_Checklist_v2_merged.xlsx
+++ b/TC_Manager_Regression_Checklist_v2_merged.xlsx
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P249"/>
+  <dimension ref="A1:P252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -15803,7 +15803,6 @@
           <t>미수행/N-A 노출</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
           <t>기능</t>
@@ -15827,14 +15826,11 @@
 3. PASS Rate 카드 아래에 분모가 실행 건수임이 표기된다.</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
           <t>높음</t>
@@ -15872,7 +15868,6 @@
           <t>미수행 컬럼</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>기능</t>
@@ -15895,14 +15890,11 @@
 2. 각 행에서 PASS+FAIL+BLOCK+N-A+미수행 합이 Total 과 같다.</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
           <t>높음</t>
@@ -15940,7 +15932,6 @@
           <t>카테고리 표 컬럼</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
           <t>기능</t>
@@ -15963,14 +15954,11 @@
 2. 표가 페이지 폭을 넘지 않는다.</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
         <is>
           <t>중간</t>
@@ -15979,6 +15967,212 @@
       <c r="P249" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TC-EXP-001</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TC 관리</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>TC 0건 + 시트 분리</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>TC 가 한 건도 없는 프로젝트</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>1. TC 관리 탭에서 Excel Export 를 연다.
+2. "시트 분리 (시트별 탭)" 를 고른다.
+3. 다운로드를 누른다.</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>1. 500 오류 없이 파일이 내려온다.
+2. 파일에 "Test Cases" 시트 한 장이 있고 헤더가 있다.</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TC-EXP-002</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TC 관리</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>시트명 31자 초과</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>앞 31자가 같고 뒤가 다른 시트 2개에 각각 TC 가 있음</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>1. 시트 분리로 내보낸다.
+2. 받은 파일의 탭 이름을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>1. 모든 탭 이름이 31자 이하다.
+2. 탭 이름이 서로 겹치지 않는다.
+3. 엑셀이 복구 경고 없이 파일을 연다.</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TC-EXP-003</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>TC 관리</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Excel Export</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>엑셀 금지 문자 시트명</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>시트명이 금지 문자(* ? [ ] : / \)로만 이뤄진 시트에 TC 가 있음</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>1. 시트 분리로 내보낸다.
+2. 탭 이름을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>1. 오류 없이 내려온다.
+2. 탭 이름이 비어 있지 않다.</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
